--- a/assets/tourist_nights_2024_by_TG_intensity.xlsx
+++ b/assets/tourist_nights_2024_by_TG_intensity.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workz\geo\assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AA0014-7DFF-4B82-B66F-1BE5FB43DB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -412,8 +418,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,17 +478,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -520,7 +534,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -554,6 +568,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -588,9 +603,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -763,11 +779,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +814,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -810,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -824,7 +848,7 @@
         <v>3506</v>
       </c>
       <c r="E3">
-        <v>4.394585109049882</v>
+        <v>4.3945851090498822</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -833,7 +857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -853,7 +877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -867,7 +891,7 @@
         <v>2969</v>
       </c>
       <c r="E5">
-        <v>7.968330649490047</v>
+        <v>7.9683306494900474</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -876,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -896,7 +920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -916,7 +940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -924,7 +948,7 @@
         <v>75</v>
       </c>
       <c r="C8">
-        <v>141.7</v>
+        <v>141.69999999999999</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -936,7 +960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -956,7 +980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -964,7 +988,7 @@
         <v>77</v>
       </c>
       <c r="C10">
-        <v>153.3</v>
+        <v>153.30000000000001</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -976,7 +1000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -999,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1019,7 +1043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1039,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1053,7 +1077,7 @@
         <v>3602</v>
       </c>
       <c r="E14">
-        <v>7.469929489838226</v>
+        <v>7.4699294898382256</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -1062,7 +1086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1076,7 +1100,7 @@
         <v>9793</v>
       </c>
       <c r="E15">
-        <v>22.80624126688397</v>
+        <v>22.806241266883969</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -1085,7 +1109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1099,7 +1123,7 @@
         <v>585</v>
       </c>
       <c r="E16">
-        <v>1.577244540307356</v>
+        <v>1.5772445403073561</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -1108,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1122,7 +1146,7 @@
         <v>111916</v>
       </c>
       <c r="E17">
-        <v>408.1546316557242</v>
+        <v>408.15463165572419</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -1131,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1145,7 +1169,7 @@
         <v>170948</v>
       </c>
       <c r="E18">
-        <v>624.5816587504544</v>
+        <v>624.58165875045438</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -1154,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1174,7 +1198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1188,7 +1212,7 @@
         <v>1207</v>
       </c>
       <c r="E20">
-        <v>1.802568697729985</v>
+        <v>1.8025686977299851</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -1197,7 +1221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1217,7 +1241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1225,13 +1249,13 @@
         <v>89</v>
       </c>
       <c r="C22">
-        <v>268.9</v>
+        <v>268.89999999999998</v>
       </c>
       <c r="D22">
         <v>2458</v>
       </c>
       <c r="E22">
-        <v>9.140944589066534</v>
+        <v>9.1409445890665335</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1240,7 +1264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1254,7 +1278,7 @@
         <v>2138</v>
       </c>
       <c r="E23">
-        <v>8.673427991886374</v>
+        <v>8.6734279918863741</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1263,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1283,7 +1307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1297,7 +1321,7 @@
         <v>1091</v>
       </c>
       <c r="E25">
-        <v>5.358546168958717</v>
+        <v>5.3585461689587168</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1306,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1314,13 +1338,13 @@
         <v>93</v>
       </c>
       <c r="C26">
-        <v>142.8</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26">
-        <v>0.01400560224089626</v>
+        <v>1.400560224089626E-2</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1329,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1352,7 +1376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1366,7 +1390,7 @@
         <v>1960</v>
       </c>
       <c r="E28">
-        <v>5.19067796610168</v>
+        <v>5.1906779661016804</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1375,7 +1399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1395,7 +1419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1409,7 +1433,7 @@
         <v>6251</v>
       </c>
       <c r="E30">
-        <v>24.46575342465744</v>
+        <v>24.465753424657439</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1418,7 +1442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1438,7 +1462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1452,7 +1476,7 @@
         <v>124</v>
       </c>
       <c r="E32">
-        <v>1.481481481481464</v>
+        <v>1.4814814814814641</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1461,7 +1485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1469,13 +1493,13 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>128.3</v>
+        <v>128.30000000000001</v>
       </c>
       <c r="D33">
         <v>2114</v>
       </c>
       <c r="E33">
-        <v>16.47700701480891</v>
+        <v>16.477007014808908</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1484,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -1504,7 +1528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1527,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1550,7 +1574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1558,7 +1582,7 @@
         <v>104</v>
       </c>
       <c r="C37">
-        <v>162.3</v>
+        <v>162.30000000000001</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1570,7 +1594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1590,7 +1614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1610,7 +1634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1624,7 +1648,7 @@
         <v>157</v>
       </c>
       <c r="E40">
-        <v>0.425358981305878</v>
+        <v>0.42535898130587801</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -1633,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -1647,7 +1671,7 @@
         <v>157</v>
       </c>
       <c r="E41">
-        <v>0.7302325581395315</v>
+        <v>0.73023255813953147</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -1656,7 +1680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -1676,7 +1700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -1690,7 +1714,7 @@
         <v>9844</v>
       </c>
       <c r="E43">
-        <v>30.12239902080774</v>
+        <v>30.122399020807741</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -1699,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1713,7 +1737,7 @@
         <v>4171</v>
       </c>
       <c r="E44">
-        <v>36.1125541125538</v>
+        <v>36.112554112553802</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -1722,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1745,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1768,7 +1792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1782,7 +1806,7 @@
         <v>36</v>
       </c>
       <c r="E47">
-        <v>0.3684749232343872</v>
+        <v>0.36847492323438719</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -1791,7 +1815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -1805,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="E48">
-        <v>0.02150537634408591</v>
+        <v>2.1505376344085909E-2</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -1814,7 +1838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -1834,7 +1858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -1842,7 +1866,7 @@
         <v>117</v>
       </c>
       <c r="C50">
-        <v>66.09999999999999</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1854,7 +1878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -1874,7 +1898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -1888,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -1908,7 +1932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -1928,7 +1952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -1942,7 +1966,7 @@
         <v>1735</v>
       </c>
       <c r="E55">
-        <v>8.994297563504359</v>
+        <v>8.9942975635043592</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -1951,7 +1975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -1965,7 +1989,7 @@
         <v>1332</v>
       </c>
       <c r="E56">
-        <v>6.35799522673028</v>
+        <v>6.3579952267302797</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -1974,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -1988,7 +2012,7 @@
         <v>6952</v>
       </c>
       <c r="E57">
-        <v>16.37691401648995</v>
+        <v>16.376914016489948</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -1997,7 +2021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -2005,7 +2029,7 @@
         <v>125</v>
       </c>
       <c r="C58">
-        <v>327.4</v>
+        <v>327.39999999999998</v>
       </c>
       <c r="D58">
         <v>781801</v>
@@ -2020,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -2034,7 +2058,7 @@
         <v>6002</v>
       </c>
       <c r="E59">
-        <v>34.3560389238693</v>
+        <v>34.356038923869299</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -2043,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -2066,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -2080,7 +2104,7 @@
         <v>105150</v>
       </c>
       <c r="E61">
-        <v>395.7470831765133</v>
+        <v>395.74708317651329</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -2089,7 +2113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -2097,13 +2121,13 @@
         <v>129</v>
       </c>
       <c r="C62">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D62">
         <v>684</v>
       </c>
       <c r="E62">
-        <v>36.77419354838512</v>
+        <v>36.774193548385121</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -2112,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>68</v>
       </c>
